--- a/outputs/evaluation/decision/v1/CF_M05/run_2/CF_M05_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_2/CF_M05_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3333</v>
+        <v>0.625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1818</v>
+        <v>0.3846</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8276</v>
+        <v>0.8502</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6667</v>
+        <v>0.6</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.9701</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3333</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1818</v>
+        <v>0.3846</v>
       </c>
     </row>
     <row r="9">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -752,34 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" t="n">
         <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,16 +974,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AD11</t>
+          <t>CF_M05_AD03</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7675</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1009,75 +1009,75 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.8804</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>The application is designed, deployed, and executed using cloud services instead of local or physical servers. The use of this type of architecture allows high scalability, availability, and accessibility. AWS is a consolidated cloud platform with robust services and a reliable infrastructure.</t>
+          <t>The portal microservice has the main function of offering a centralized interface for access to the different VWGS applications.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Tecnologia cloud, R_43, R_44</t>
+          <t>R_06, R_10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_17, AU_18, AU_19</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>60, 81</t>
+          <t>57</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
+          <t>CF_M05_C01, *CF_M05_C12</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_AD06</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.8214</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -1097,48 +1097,305 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The application has an architecture based on microservices, consisting of dividing the system into a set of small, independent, and autonomous services. This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
+          <t>It offers flexibility, scalability, and cost reduction, as it eliminates the need for local infrastructure.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Microserveis, R_45</t>
+          <t>Technology cloud</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M05_AD01</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>8, 56</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>56</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8651</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated, clarifying roles, avoiding unnecessary coupling, and facilitating testing, reusing, and maintaining the code over time.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>AU_14, P_04</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9018</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Amazon EKS allows automating the deployment, scaling, and management of applications running in containers, executing thousands of containers on different servers and ensuring high availability.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C_06, C_07</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>AU_18, AU_19</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,136 +1457,101 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client and the server. The client has been developed with Angular, implementing a Single-Page Application (SPA) that renders dynamic views and manages internal navigation without having to reload the page, improving fluidity of use. For the server, Spring Boot has been used, which provides a platform for exposing a REST API.</t>
+          <t>This microservice has the main function of routing all communications to the corresponding microservice within the system architecture, acting as a central traffic management point.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_01, C_02, C_04</t>
+          <t>Bus d’integració</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01, AU_13, AU_14</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD03</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7232</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services. The ViewModel acts as an intermediary between the View and the Model, providing the data that the view needs and managing the user's actions.</t>
+          <t>The Access Control microservice has as its main objective the management of user authentication and their permissions within the application.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_02, C_04</t>
+          <t>R_48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>62, 64</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6886</v>
+        <v>0.7119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated: the presentation layer receives requests and builds responses, the business logic layer applies the domain rules, the data access layer interacts with the database and the domain layer defines the data model.</t>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services, which allows building modern single-page applications (SPA) that render dynamic views and manage internal navigation without having to reload the page, improving fluidity of use.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_09</t>
+          <t>C_02, C_04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_13, P_03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>61, 62</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AD08</t>
+          <t>CF_M05_AD09</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7407</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>A transversal contract layer is added that separates the internal model from the external representation of the API. This structure clarifies roles, avoids unnecessary coupling, and facilitates testing, reusing, and maintaining the code over time.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C_09</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CF_M05_AD08</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.729</v>
+        <v>0.7437</v>
       </c>
     </row>
   </sheetData>
@@ -1343,7 +1565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1409,65 +1631,65 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6479</v>
+        <v>0.7007</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD03</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CF_M05_C01, *CF_M05_C12</t>
+          <t>*CF_M05_C11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6561</v>
+        <v>0.7119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C11</t>
+          <t>*CF_M05_C13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1475,102 +1697,102 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6727</v>
+        <v>0.6888</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>*CF_M05_C15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6607</v>
+        <v>0.6819</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD06</t>
+          <t>CF_M05_AD08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_P05</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.7674</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1578,106 +1800,73 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.6953</v>
+        <v>0.7437</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AD08</t>
+          <t>CF_M05_AD10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+          <t>*CF_M05_C14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.7407</v>
+        <v>0.7173</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>*CF_M05_C18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7232</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AD10</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>*CF_M05_C14</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>77</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AD_03</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0.7177</v>
+        <v>0.767</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/decision/v1/CF_M05/run_2/CF_M05_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_2/CF_M05_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.625</v>
+        <v>0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3846</v>
+        <v>0.0769</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8502</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4</v>
+        <v>0.0833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6</v>
+        <v>0.1667</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9701</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.625</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3846</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,31 +755,31 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>12</v>
-      </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -792,31 +792,31 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,23 +979,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AD03</t>
+          <t>CF_M05_AD01</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.843</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1009,393 +1009,51 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.1667</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8804</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>The portal microservice has the main function of offering a centralized interface for access to the different VWGS applications.</t>
+          <t>The application has an architecture based on microservices, consisting of dividing the system into a set of small, independent, and autonomous services.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R_06, R_10</t>
+          <t>C_05, C_06, C_07, R_43, R_44, R_45, R_46, R_47, R_48, R_49, R_50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>P_02, AU_08, AU_09, AU_10, AU_11, AU_12</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55, 56</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M05_C01, *CF_M05_C12</t>
+          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CF_M05_AD06</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.8214</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>It offers flexibility, scalability, and cost reduction, as it eliminates the need for local infrastructure.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Technology cloud</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>CF_M05_P05</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CF_M05_AD01</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>CF_M05_P01</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
         <v>56</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CF_M05_AD12</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.8651</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated, clarifying roles, avoiding unnecessary coupling, and facilitating testing, reusing, and maintaining the code over time.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>AU_14, P_04</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>*CF_M05_C14</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CF_M05_AD11</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9018</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Amazon EKS allows automating the deployment, scaling, and management of applications running in containers, executing thousands of containers on different servers and ensuring high availability.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>C_06, C_07</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>AU_18, AU_19</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CF_M05_AU07</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,106 +1110,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This microservice has the main function of routing all communications to the corresponding microservice within the system architecture, acting as a central traffic management point.</t>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bus d’integració</t>
+          <t>C_01, C_02, C_04, R_33, R_34, R_35, R_39, R_40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_13, P_03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M05_AD03</t>
+          <t>CF_M05_AD10</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.703</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Access Control microservice has as its main objective the management of user authentication and their permissions within the application.</t>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R_48</t>
+          <t>C_05, C_06, C_07, R_41, R_42, R_43, R_44, R_45, R_46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_14, P_04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD12</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7119</v>
+        <v>0.7287</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services, which allows building modern single-page applications (SPA) that render dynamic views and manage internal navigation without having to reload the page, improving fluidity of use.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, that formulates service requests, and the server, that receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_02, C_04</t>
+          <t>C_05, C_06, R_43, R_44, R_45, R_46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AU_13, P_03</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>61, 62</t>
+          <t>60, 61</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD08</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7437</v>
+        <v>0.7099</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AWS is a consolidated cloud platform with robust services and a reliable infrastructure. One of the great advantages of AWS is that it has a very wide selection of services: from the deployment of servers and databases, to AI, storage, security, and specific services for sectors. This diversity makes it easy to adapt to the needs of the project, allows growing and scaling the project in an agile way and eliminates the need to look for other platforms when requirements evolve. For this reason, AWS was chosen instead of other options like Google Cloud Platform or Microsoft Azure. Having so many services available leaves the effort to be concentrated on the development of the solution, without having to invest extra time in infrastructure issues. Another reason why AWS was chosen was that this platform invests heavily in security and certifications, manages multiple security levels and offers tools to protect data and infrastructure, facilitating compliance with legal regulations and international standards.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C_06, C_07, R_43, R_44, R_45, R_46</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU_17, AU_18, AU_19</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>81, 82</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD13</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7302</v>
       </c>
     </row>
   </sheetData>
@@ -1565,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,36 +1324,36 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7007</v>
+        <v>0.6086</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M05_C11</t>
+          <t>CF_M05_C01, *CF_M05_C12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1668,28 +1361,28 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7119</v>
+        <v>0.6424</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>*CF_M05_C11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1697,176 +1390,308 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6888</v>
+        <v>0.6889</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>*CF_M05_C13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6819</v>
+        <v>0.6181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD08</t>
+          <t>CF_M05_AD06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_P05</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.745</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>*CF_M05_C15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.7437</v>
+        <v>0.7007</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>*CF_M05_C14</t>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.7173</v>
+        <v>0.7171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>CF_M05_AD09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>76</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6763</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AD10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>77</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>81</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7136</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>78</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7287</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>CF_M05_AD13</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>*CF_M05_C18</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E13" t="n">
         <v>82</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.767</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7302</v>
       </c>
     </row>
   </sheetData>
